--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T06:12:55+00:00</t>
+    <t>2026-10-12T12:45:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:45:08+00:00</t>
+    <t>2026-10-12T17:47:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T17:47:09+00:00</t>
+    <t>2026-10-13T16:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T16:03:24+00:00</t>
+    <t>2026-10-14T07:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T07:51:23+00:00</t>
+    <t>2026-10-14T10:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T10:33:13+00:00</t>
+    <t>2026-10-14T18:50:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T18:50:32+00:00</t>
+    <t>2026-10-14T21:19:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T21:19:26+00:00</t>
+    <t>2026-10-15T08:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T08:30:16+00:00</t>
+    <t>2026-10-15T11:48:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:48:20+00:00</t>
+    <t>2026-10-15T13:39:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:39:50+00:00</t>
+    <t>2026-10-15T16:16:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:16:55+00:00</t>
+    <t>2026-10-15T16:39:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:39:56+00:00</t>
+    <t>2026-10-16T09:51:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:51:31+00:00</t>
+    <t>2026-10-16T10:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T10:13:15+00:00</t>
+    <t>2026-10-16T11:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T11:00:25+00:00</t>
+    <t>2026-10-17T00:02:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T00:02:12+00:00</t>
+    <t>2026-10-17T19:55:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -588,7 +588,7 @@
     <t>A human readable description of the error issue SHOULD be placed in details.text.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/at-emed-operationoutcome-details</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/at-elga-emed-operationoutcome-details</t>
   </si>
   <si>
     <t>ERR-5</t>
@@ -981,7 +981,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="38.43359375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="60.73828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="64.66796875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T19:55:22+00:00</t>
+    <t>2026-10-18T08:01:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T08:01:40+00:00</t>
+    <t>2026-10-18T09:33:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T09:33:28+00:00</t>
+    <t>2026-10-18T20:24:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T20:24:08+00:00</t>
+    <t>2026-10-19T15:55:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T15:55:36+00:00</t>
+    <t>2026-10-19T16:11:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T16:11:48+00:00</t>
+    <t>2026-10-19T18:28:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T18:28:35+00:00</t>
+    <t>2026-10-20T08:04:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T08:04:36+00:00</t>
+    <t>2026-10-20T12:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T12:30:11+00:00</t>
+    <t>2026-10-20T15:36:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T15:36:59+00:00</t>
+    <t>2026-10-20T16:38:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T16:38:16+00:00</t>
+    <t>2026-10-20T17:05:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T17:05:58+00:00</t>
+    <t>2026-10-21T09:29:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:29:04+00:00</t>
+    <t>2026-10-21T09:52:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:52:38+00:00</t>
+    <t>2026-10-21T10:08:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T10:08:52+00:00</t>
+    <t>2026-10-21T11:24:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T11:24:22+00:00</t>
+    <t>2026-10-21T12:17:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T12:17:05+00:00</t>
+    <t>2026-10-21T14:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T14:17:59+00:00</t>
+    <t>2026-10-21T15:07:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:07:55+00:00</t>
+    <t>2026-10-21T15:51:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:51:37+00:00</t>
+    <t>2026-10-22T07:17:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:17:51+00:00</t>
+    <t>2026-10-22T07:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:44:55+00:00</t>
+    <t>2026-10-22T08:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T08:46:49+00:00</t>
+    <t>2026-10-22T09:37:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:37:30+00:00</t>
+    <t>2026-10-22T09:48:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:48:24+00:00</t>
+    <t>2026-10-22T11:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T11:28:40+00:00</t>
+    <t>2026-10-22T12:03:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:03:52+00:00</t>
+    <t>2026-10-22T12:14:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:14:48+00:00</t>
+    <t>2026-10-22T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T18:22:51+00:00</t>
+    <t>2026-10-23T11:54:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T11:54:03+00:00</t>
+    <t>2026-10-23T12:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T12:23:07+00:00</t>
+    <t>2026-10-23T13:54:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T13:54:21+00:00</t>
+    <t>2026-10-23T16:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T16:16:05+00:00</t>
+    <t>2026-10-26T11:42:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T11:42:48+00:00</t>
+    <t>2026-10-26T12:04:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T12:04:07+00:00</t>
+    <t>2026-10-26T13:41:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:41:17+00:00</t>
+    <t>2026-10-26T13:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:57:36+00:00</t>
+    <t>2026-10-26T16:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:01:21+00:00</t>
+    <t>2026-10-26T16:19:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:19:19+00:00</t>
+    <t>2026-10-26T17:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:11:45+00:00</t>
+    <t>2026-10-26T17:20:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:20:41+00:00</t>
+    <t>2026-10-26T17:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:56:13+00:00</t>
+    <t>2026-10-26T18:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T18:36:30+00:00</t>
+    <t>2026-10-26T20:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:24:37+00:00</t>
+    <t>2026-10-26T20:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:58:24+00:00</t>
+    <t>2026-10-26T21:10:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T21:10:14+00:00</t>
+    <t>2026-10-27T12:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:33:12+00:00</t>
+    <t>2026-10-27T12:53:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:53:20+00:00</t>
+    <t>2026-10-27T13:46:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T13:46:50+00:00</t>
+    <t>2026-10-27T19:38:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T19:38:06+00:00</t>
+    <t>2026-10-27T20:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T20:05:18+00:00</t>
+    <t>2026-10-27T21:19:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T21:19:55+00:00</t>
+    <t>2026-10-28T09:21:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T09:21:39+00:00</t>
+    <t>2026-10-28T10:28:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T10:28:56+00:00</t>
+    <t>2026-10-28T15:47:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T15:47:56+00:00</t>
+    <t>2026-10-28T21:33:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T21:33:03+00:00</t>
+    <t>2026-10-29T07:35:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:35:42+00:00</t>
+    <t>2026-10-29T08:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:12:50+00:00</t>
+    <t>2026-10-29T08:46:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:46:29+00:00</t>
+    <t>2026-10-29T10:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:03:24+00:00</t>
+    <t>2026-10-29T10:46:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:46:22+00:00</t>
+    <t>2026-10-29T11:16:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T11:16:49+00:00</t>
+    <t>2026-10-29T12:53:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T12:53:50+00:00</t>
+    <t>2026-10-29T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:18:54+00:00</t>
+    <t>2026-10-29T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -588,7 +588,7 @@
     <t>A human readable description of the error issue SHOULD be placed in details.text.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/at-elga-emed-operationoutcome-details</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/at-elga-emed-valueset-operationoutcome-details-vs</t>
   </si>
   <si>
     <t>ERR-5</t>
@@ -981,7 +981,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="38.43359375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="64.66796875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="74.25" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:53:17+00:00</t>
+    <t>2026-10-29T14:20:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-operationoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T14:20:15+00:00</t>
+    <t>2026-10-29T14:50:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
